--- a/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
+++ b/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$M$91</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$M$83</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>90 filas de datos</t>
+          <t>82 filas de datos</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Bajo riesgo de sesgo</t>
+          <t>Algunas preocupaciones</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -2693,17 +2693,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>R436ad33f7e</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Single-arm, open-labelled, safety and tolerability of intrabronchial a (BMJ open respiratory research, 2023)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Sin información para juzgar</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Sin grupo comparador (diseño de un solo brazo).</t>
+          <t>Sin grupo control. “In 77.7% (n = 14) of the cases, a favorable clinical outcome of infection remission or recovery was seen.”</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>R436ad33f7e</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Single-arm, open-labelled, safety and tolerability of intrabronchial a (BMJ open respiratory research, 2023)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Criterios de inclusión/exclusión definidos, pero muestra muy pequeña y seleccionada (máx. 10 niños).</t>
+          <t>“In 53 cases the phage screening process resulted in finding a potential potent phage. Yet, only 20 treatments in 18 patients were…”</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2827,17 +2827,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>R436ad33f7e</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Single-arm, open-labelled, safety and tolerability of intrabronchial a (BMJ open respiratory research, 2023)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Intervención claramente descrita (fagos intrabronquiales + nebulizados).</t>
+          <t>Intervención claramente descrita (terapia fágica personalizada).</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2894,17 +2894,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>R436ad33f7e</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Single-arm, open-labelled, safety and tolerability of intrabronchial a (BMJ open respiratory research, 2023)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Estudio abierto, posibles co-intervenciones.</t>
+          <t>Uso compasivo, tratamientos individualizados + antibióticos concurrentes.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2961,17 +2961,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>R436ad33f7e</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Single-arm, open-labelled, safety and tolerability of intrabronchial a (BMJ open respiratory research, 2023)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Sin información para juzgar</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Es un protocolo; aún no hay resultados.</t>
+          <t>“The microbiological outcomes in cases where no cultures were obtained were considered indeterminate.”</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>R436ad33f7e</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Single-arm, open-labelled, safety and tolerability of intrabronchial a (BMJ open respiratory research, 2023)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Estudio abierto; desenlaces de seguridad evaluados sin cegamiento.</t>
+          <t>“Clinical and microbiological outcomes were evaluated by an infectious diseases physician.”</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3095,17 +3095,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>R436ad33f7e</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Single-arm, open-labelled, safety and tolerability of intrabronchial a (BMJ open respiratory research, 2023)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Protocolo registrado (ACTRN12622000767707), pero es piloto.</t>
+          <t>No hay protocolo de análisis pre-registrado.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3162,17 +3162,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EST-063</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>R436ad33f7e</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Single-arm, open-labelled, safety and tolerability of intrabronchial a (BMJ open respiratory research, 2023)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3229,17 +3229,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Sin grupo control. “In 77.7% (n = 14) of the cases, a favorable clinical outcome of infection remission or recovery was seen.”</t>
+          <t>Sin grupo control. Imposible separar el efecto del fago de otros factores.</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Riesgo grave</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>“In 53 cases the phage screening process resulted in finding a potential potent phage. Yet, only 20 treatments in 18 patients were…”</t>
+          <t>Pacientes seleccionados de la Unidad de Terapia Fágica (casos crónicos, sensibles a fagos).</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Intervención claramente descrita (terapia fágica personalizada).</t>
+          <t>Administración intravesical ± intravaginal de fagos específicos claramente descrita.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3430,17 +3430,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Uso compasivo, tratamientos individualizados + antibióticos concurrentes.</t>
+          <t>Tratamientos personalizados, duración corta (3 días), posibles co-intervenciones.</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3497,17 +3497,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>“The microbiological outcomes in cases where no cultures were obtained were considered indeterminate.”</t>
+          <t>Se reportan los 15 pacientes. Algunos datos de carga bacteriana incompletos.</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>“Clinical and microbiological outcomes were evaluated by an infectious diseases physician.”</t>
+          <t>Tasa K (laboratorio objetivo). Resultados clínicos abiertos y sin criterios estandarizados rigurosos.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3631,17 +3631,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>No hay protocolo de análisis pre-registrado.</t>
+          <t>Enfoque principal en inmunogenicidad. Resultados clínicos descriptivos.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3698,17 +3698,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Sin grupo control. Imposible separar el efecto del fago de otros factores.</t>
+          <t>“eradication was 70% less probable when no concomitant antibiotics were used (odds ratio = 0.3; 95% confidence interval = 0.127–0.749).”</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3832,17 +3832,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Pacientes seleccionados de la Unidad de Terapia Fágica (casos crónicos, sensibles a fagos).</t>
+          <t>“1,066 BT requests were submitted to the QAMH. These requests resulted in 100 BT cases (9.4%).”</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3899,17 +3899,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Administración intravesical ± intravaginal de fagos específicos claramente descrita.</t>
+          <t>Terapia fágica personalizada claramente definida.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Tratamientos personalizados, duración corta (3 días), posibles co-intervenciones.</t>
+          <t>Tratamientos heterogéneos (diferentes fagos, vías, co-intervenciones).</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Se reportan los 15 pacientes. Algunos datos de carga bacteriana incompletos.</t>
+          <t>Algunos desenlaces solo evaluados en subgrupos (16, 10, 13 pacientes).</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4100,17 +4100,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4135,7 +4135,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Riesgo grave</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Tasa K (laboratorio objetivo). Resultados clínicos abiertos y sin criterios estandarizados rigurosos.</t>
+          <t>Evaluación clínica abierta por los médicos tratantes.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4167,17 +4167,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Enfoque principal en inmunogenicidad. Resultados clínicos descriptivos.</t>
+          <t>Casos consecutivos (positivo), pero sin protocolo de análisis pre-registrado detallado.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4234,17 +4234,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4301,17 +4301,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Riesgo grave</t>
+          <t>Sin información para juzgar</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>“eradication was 70% less probable when no concomitant antibiotics were used (odds ratio = 0.3; 95% confidence interval = 0.127–0.749).”</t>
+          <t>No se evalúa un efecto de tratamiento comparativo.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4368,17 +4368,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>“1,066 BT requests were submitted to the QAMH. These requests resulted in 100 BT cases (9.4%).”</t>
+          <t>Se incluyen todas las solicitudes 2013-2018. Solo 73,1% respondieron con información médica.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4435,17 +4435,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Terapia fágica personalizada claramente definida.</t>
+          <t>No hay intervención terapéutica como resultado principal.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4502,17 +4502,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Sin información para juzgar</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Tratamientos heterogéneos (diferentes fagos, vías, co-intervenciones).</t>
+          <t>No se evalúa adherencia a un tratamiento.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4569,17 +4569,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Algunos desenlaces solo evaluados en subgrupos (16, 10, 13 pacientes).</t>
+          <t>26,9% de los solicitantes no respondió con la información médica solicitada.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4636,17 +4636,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Evaluación clínica abierta por los médicos tratantes.</t>
+          <t>Clasificación de razones de rechazo realizada por el propio equipo del hospital.</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Bajo riesgo de sesgo</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Casos consecutivos (positivo), pero sin protocolo de análisis pre-registrado detallado.</t>
+          <t>Se reportan las 260 solicitudes y se explican las razones de rechazo.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Riesgo grave</t>
+          <t>Sin información para juzgar</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -4837,32 +4837,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>ROBINS-I</t>
+          <t>RoB 2 (adaptado)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sesgo por confusión</t>
+          <t>Proceso de aleatorización</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Sin información para juzgar</t>
+          <t>Bajo riesgo de sesgo</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>No se evalúa un efecto de tratamiento comparativo.</t>
+          <t>"Randomization was performed using computer-generated random numbers. Patients were allocated to either conventional therapy or conventional therapy plus topical bacteriophage therapy. Group allocation was done using sealed opaque envelopes."</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4904,32 +4904,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ROBINS-I</t>
+          <t>RoB 2 (adaptado)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sesgo en la selección de los participantes</t>
+          <t>Desviaciones de la intervención prevista</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Algunas preocupaciones</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Se incluyen todas las solicitudes 2013-2018. Solo 73,1% respondieron con información médica.</t>
+          <t>"This was a prospective, double blind, randomized study." No se detalla el cegamiento de participantes/personal respecto a la asignación; la terapia fágica tópica personalizada podría diferir en apariencia de la convencional.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4971,32 +4971,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>ROBINS-I</t>
+          <t>RoB 2 (adaptado)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sesgo en la clasificación de las intervenciones</t>
+          <t>Datos de desenlace faltantes</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>No hay intervención terapéutica como resultado principal.</t>
+          <t>"Four patients were excluded from each group as the patients died before the 28 days, and 34 patients in each group were analyzed." No se reporta análisis por intención de tratar.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5038,32 +5038,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ROBINS-I</t>
+          <t>RoB 2 (adaptado)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sesgo por desviaciones de las intervenciones previstas</t>
+          <t>Medición del desenlace</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Sin información para juzgar</t>
+          <t>Algunas preocupaciones</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>No se evalúa adherencia a un tratamiento.</t>
+          <t>"Healing was assessed using the Pressure Ulcer Scale for Healing (PUSH) tool... at baseline and on days 5, 7, 14, 21, and 28." No se menciona cegamiento de evaluadores; la clasificación de tejidos tiene componente subjetivo.</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5105,32 +5105,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ROBINS-I</t>
+          <t>RoB 2 (adaptado)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sesgo por datos faltantes</t>
+          <t>Selección del resultado notificado</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Algunas preocupaciones</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>26,9% de los solicitantes no respondió con la información médica solicitada.</t>
+          <t>"The clinical trial was registered with registration number CTRI/2024/03/064013." Endpoint primario preespecificado: evaluar eficacia de terapia fágica para úlceras por presión.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5172,42 +5172,42 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ROBINS-I</t>
+          <t>RoB 2 (adaptado)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>GLOBAL</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Sesgo en la medición de los desenlaces</t>
+          <t>Juicio global del estudio</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>dominio</t>
+          <t>global</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Algunas preocupaciones</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Clasificación de razones de rechazo realizada por el propio equipo del hospital.</t>
+          <t>[DATO FALTANTE]</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5239,17 +5239,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sesgo en la selección del resultado notificado</t>
+          <t>Sesgo por confusión</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Bajo riesgo de sesgo</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Se reportan las 260 solicitudes y se explican las razones de rechazo.</t>
+          <t>Sin grupo control + antibióticos concomitantes frecuentes.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5326,22 +5326,22 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Juicio global del estudio</t>
+          <t>Sesgo en la selección de los participantes</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>dominio</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>[DATO FALTANTE]</t>
+          <t>“Fifty requests for phage therapy were received. Customized phages were generated for 12 patients.”</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5373,32 +5373,32 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Proceso de aleatorización</t>
+          <t>Sesgo en la clasificación de las intervenciones</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>"Randomization was performed using computer-generated random numbers. Patients were allocated to either conventional therapy or conventional therapy plus topical bacteriophage therapy. Group allocation was done using sealed opaque envelopes."</t>
+          <t>Fagos personalizados claramente caracterizados.</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5440,32 +5440,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Desviaciones de la intervención prevista</t>
+          <t>Sesgo por desviaciones de las intervenciones previstas</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Algunas preocupaciones</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>"This was a prospective, double blind, randomized study." No se detalla el cegamiento de participantes/personal respecto a la asignación; la terapia fágica tópica personalizada podría diferir en apariencia de la convencional.</t>
+          <t>Tratamientos individualizados + co-intervenciones.</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5507,32 +5507,32 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Datos de desenlace faltantes</t>
+          <t>Sesgo por datos faltantes</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Bajo riesgo de sesgo</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>"Four patients were excluded from each group as the patients died before the 28 days, and 34 patients in each group were analyzed." No se reporta análisis por intención de tratar.</t>
+          <t>Algunos datos inmunológicos solo en subgrupos.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5574,32 +5574,32 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Medición del desenlace</t>
+          <t>Sesgo en la medición de los desenlaces</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Algunas preocupaciones</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>"Healing was assessed using the Pressure Ulcer Scale for Healing (PUSH) tool... at baseline and on days 5, 7, 14, 21, and 28." No se menciona cegamiento de evaluadores; la clasificación de tejidos tiene componente subjetivo.</t>
+          <t>“These responses were determined by a combination of physician judgment and patient symptom reporting.”</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5641,32 +5641,32 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Selección del resultado notificado</t>
+          <t>Sesgo en la selección del resultado notificado</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Algunas preocupaciones</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>"The clinical trial was registered with registration number CTRI/2024/03/064013." Endpoint primario preespecificado: evaluar eficacia de terapia fágica para úlceras por presión.</t>
+          <t>Se reportan resultados favorables y desfavorables.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5708,22 +5708,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5743,7 +5743,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Algunas preocupaciones</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5775,17 +5775,17 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Sin grupo control + antibióticos concomitantes frecuentes.</t>
+          <t>Sin grupo control. No se puede separar el efecto del fago de otros tratamientos concurrentes.</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5842,17 +5842,17 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Riesgo grave</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>“Fifty requests for phage therapy were received. Customized phages were generated for 12 patients.”</t>
+          <t>Pacientes seleccionados de la Unidad de Terapia Fágica (infecciones óseas, tejidos blandos o vías respiratorias altas).</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -5909,17 +5909,17 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Fagos personalizados claramente caracterizados.</t>
+          <t>Fagos Staph_1N o Staph_A5L, vía local o local+oral, claramente descritos.</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5976,17 +5976,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Tratamientos individualizados + co-intervenciones.</t>
+          <t>Tratamientos personalizados, duración variable (hasta 8 semanas).</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6043,17 +6043,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Algunos datos inmunológicos solo en subgrupos.</t>
+          <t>Se reportan los 27 pacientes. Algunos datos de seguimiento incompletos.</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6110,17 +6110,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>“These responses were determined by a combination of physician judgment and patient symptom reporting.”</t>
+          <t>Tasa K (laboratorio objetivo). Resultados clínicos descriptivos y abiertos.</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6177,17 +6177,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Se reportan resultados favorables y desfavorables.</t>
+          <t>Enfoque principal en el timing de aparición de anticuerpos.</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6244,17 +6244,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -6303,544 +6303,8 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Sesgo por confusión</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Riesgo grave</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Sin grupo control. No se puede separar el efecto del fago de otros tratamientos concurrentes.</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Sesgo en la selección de los participantes</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>Riesgo moderado</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Pacientes seleccionados de la Unidad de Terapia Fágica (infecciones óseas, tejidos blandos o vías respiratorias altas).</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Sesgo en la clasificación de las intervenciones</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>Bajo riesgo de sesgo</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Fagos Staph_1N o Staph_A5L, vía local o local+oral, claramente descritos.</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Sesgo por desviaciones de las intervenciones previstas</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Riesgo moderado</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Tratamientos personalizados, duración variable (hasta 8 semanas).</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Sesgo por datos faltantes</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>Riesgo moderado</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Se reportan los 27 pacientes. Algunos datos de seguimiento incompletos.</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Sesgo en la medición de los desenlaces</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Riesgo grave</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Tasa K (laboratorio objetivo). Resultados clínicos descriptivos y abiertos.</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>D7</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Sesgo en la selección del resultado notificado</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Riesgo moderado</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Enfoque principal en el timing de aparición de anticuerpos.</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>GLOBAL</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Juicio global del estudio</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Riesgo grave</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>[DATO FALTANTE]</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M91"/>
+  <autoFilter ref="A1:M83"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
+++ b/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
@@ -709,7 +709,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
+++ b/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$M$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$M$75</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>82 filas de datos</t>
+          <t>74 filas de datos</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2157,17 +2157,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rd343ee57dd</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy in women with chronic recurrent cystitis caused  (Current Urology, 2025)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>“Following patient exclusion, a sequence of random numbers was generated by computer and then assigned to each investigated group.” → No describe el método real de asignación ni hay ajuste por confusores.</t>
+          <t>Sin grupo control. “In 77.7% (n = 14) of the cases, a favorable clinical outcome of infection remission or recovery was seen.”</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2224,17 +2224,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Rd343ee57dd</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy in women with chronic recurrent cystitis caused  (Current Urology, 2025)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2259,7 +2259,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>“Initially, 217 female patients were presented… Those who did not meet the criteria inclusions were excluded, and 178 female patients were included in the final analysis.”</t>
+          <t>“In 53 cases the phage screening process resulted in finding a potential potent phage. Yet, only 20 treatments in 18 patients were…”</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2291,17 +2291,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rd343ee57dd</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy in women with chronic recurrent cystitis caused  (Current Urology, 2025)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>“group I: received bacteriophage (Sextaphage) therapy alone; group II: received a combination of bacteriophages (Sextaphage) and furazidin; group III: … and group IV: received furazidin and cefixime (without bacteriophage).”</t>
+          <t>Intervención claramente descrita (terapia fágica personalizada).</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rd343ee57dd</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy in women with chronic recurrent cystitis caused  (Current Urology, 2025)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2403,7 +2403,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>No hay información detallada sobre adherencia ni co-intervenciones.</t>
+          <t>Uso compasivo, tratamientos individualizados + antibióticos concurrentes.</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2425,17 +2425,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rd343ee57dd</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy in women with chronic recurrent cystitis caused  (Current Urology, 2025)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>El flowchart muestra “Withdrawn” en varios grupos; no se detalla el manejo de los datos faltantes.</t>
+          <t>“The microbiological outcomes in cases where no cultures were obtained were considered indeterminate.”</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2492,17 +2492,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Rd343ee57dd</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy in women with chronic recurrent cystitis caused  (Current Urology, 2025)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Desenlaces primarios = ACSS y VAS (subjetivos). No se menciona cegamiento.</t>
+          <t>“Clinical and microbiological outcomes were evaluated by an infectious diseases physician.”</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2559,17 +2559,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rd343ee57dd</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy in women with chronic recurrent cystitis caused  (Current Urology, 2025)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>No se menciona registro previo del protocolo.</t>
+          <t>No hay protocolo de análisis pre-registrado.</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2626,17 +2626,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EST-055</t>
+          <t>EST-070</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rd343ee57dd</t>
+          <t>R92876627c6</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Bacteriophage therapy in women with chronic recurrent cystitis caused  (Current Urology, 2025)</t>
+          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2693,17 +2693,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Sin grupo control. “In 77.7% (n = 14) of the cases, a favorable clinical outcome of infection remission or recovery was seen.”</t>
+          <t>Sin grupo control. Imposible separar el efecto del fago de otros factores.</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Riesgo grave</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>“In 53 cases the phage screening process resulted in finding a potential potent phage. Yet, only 20 treatments in 18 patients were…”</t>
+          <t>Pacientes seleccionados de la Unidad de Terapia Fágica (casos crónicos, sensibles a fagos).</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2827,17 +2827,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Intervención claramente descrita (terapia fágica personalizada).</t>
+          <t>Administración intravesical ± intravaginal de fagos específicos claramente descrita.</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2894,17 +2894,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Uso compasivo, tratamientos individualizados + antibióticos concurrentes.</t>
+          <t>Tratamientos personalizados, duración corta (3 días), posibles co-intervenciones.</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2961,17 +2961,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>“The microbiological outcomes in cases where no cultures were obtained were considered indeterminate.”</t>
+          <t>Se reportan los 15 pacientes. Algunos datos de carga bacteriana incompletos.</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3028,17 +3028,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>“Clinical and microbiological outcomes were evaluated by an infectious diseases physician.”</t>
+          <t>Tasa K (laboratorio objetivo). Resultados clínicos abiertos y sin criterios estandarizados rigurosos.</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3095,17 +3095,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>No hay protocolo de análisis pre-registrado.</t>
+          <t>Enfoque principal en inmunogenicidad. Resultados clínicos descriptivos.</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3162,17 +3162,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EST-070</t>
+          <t>EST-096</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>R92876627c6</t>
+          <t>Re198b54d4f</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Compassionate Use of Bacteriophages for Failed Persistent Infections D (Open Forum Infectious Diseases, 2023)</t>
+          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -3229,17 +3229,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Sin grupo control. Imposible separar el efecto del fago de otros factores.</t>
+          <t>“eradication was 70% less probable when no concomitant antibiotics were used (odds ratio = 0.3; 95% confidence interval = 0.127–0.749).”</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Pacientes seleccionados de la Unidad de Terapia Fágica (casos crónicos, sensibles a fagos).</t>
+          <t>“1,066 BT requests were submitted to the QAMH. These requests resulted in 100 BT cases (9.4%).”</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3363,17 +3363,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Administración intravesical ± intravaginal de fagos específicos claramente descrita.</t>
+          <t>Terapia fágica personalizada claramente definida.</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3430,17 +3430,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Tratamientos personalizados, duración corta (3 días), posibles co-intervenciones.</t>
+          <t>Tratamientos heterogéneos (diferentes fagos, vías, co-intervenciones).</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3497,17 +3497,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Se reportan los 15 pacientes. Algunos datos de carga bacteriana incompletos.</t>
+          <t>Algunos desenlaces solo evaluados en subgrupos (16, 10, 13 pacientes).</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Riesgo grave</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Tasa K (laboratorio objetivo). Resultados clínicos abiertos y sin criterios estandarizados rigurosos.</t>
+          <t>Evaluación clínica abierta por los médicos tratantes.</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3631,17 +3631,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Enfoque principal en inmunogenicidad. Resultados clínicos descriptivos.</t>
+          <t>Casos consecutivos (positivo), pero sin protocolo de análisis pre-registrado detallado.</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3698,17 +3698,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EST-096</t>
+          <t>EST-108</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Re198b54d4f</t>
+          <t>R3841f327ba</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Low immunogenicity of intravesical phage therapy for urogenitary tract (Antibiotics, 2021)</t>
+          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3800,7 +3800,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Riesgo grave</t>
+          <t>Sin información para juzgar</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>“eradication was 70% less probable when no concomitant antibiotics were used (odds ratio = 0.3; 95% confidence interval = 0.127–0.749).”</t>
+          <t>No se evalúa un efecto de tratamiento comparativo.</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3832,17 +3832,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>“1,066 BT requests were submitted to the QAMH. These requests resulted in 100 BT cases (9.4%).”</t>
+          <t>Se incluyen todas las solicitudes 2013-2018. Solo 73,1% respondieron con información médica.</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3899,17 +3899,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Terapia fágica personalizada claramente definida.</t>
+          <t>No hay intervención terapéutica como resultado principal.</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Sin información para juzgar</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Tratamientos heterogéneos (diferentes fagos, vías, co-intervenciones).</t>
+          <t>No se evalúa adherencia a un tratamiento.</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4033,17 +4033,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Algunos desenlaces solo evaluados en subgrupos (16, 10, 13 pacientes).</t>
+          <t>26,9% de los solicitantes no respondió con la información médica solicitada.</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4100,17 +4100,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Evaluación clínica abierta por los médicos tratantes.</t>
+          <t>Clasificación de razones de rechazo realizada por el propio equipo del hospital.</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4167,17 +4167,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -4202,7 +4202,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Bajo riesgo de sesgo</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Casos consecutivos (positivo), pero sin protocolo de análisis pre-registrado detallado.</t>
+          <t>Se reportan las 260 solicitudes y se explican las razones de rechazo.</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4234,17 +4234,17 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EST-108</t>
+          <t>EST-116</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>R3841f327ba</t>
+          <t>Rb9ec93cff9</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Personalized bacteriophage therapy outcomes for 100 consecutive cases: (Nature microbiology, 2024)</t>
+          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4269,7 +4269,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Riesgo grave</t>
+          <t>Sin información para juzgar</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4289,7 +4289,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -4301,32 +4301,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ROBINS-I</t>
+          <t>RoB 2 (adaptado)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Sesgo por confusión</t>
+          <t>Proceso de aleatorización</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Sin información para juzgar</t>
+          <t>Bajo riesgo de sesgo</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>No se evalúa un efecto de tratamiento comparativo.</t>
+          <t>"Randomization was performed using computer-generated random numbers. Patients were allocated to either conventional therapy or conventional therapy plus topical bacteriophage therapy. Group allocation was done using sealed opaque envelopes."</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4368,32 +4368,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>ROBINS-I</t>
+          <t>RoB 2 (adaptado)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sesgo en la selección de los participantes</t>
+          <t>Desviaciones de la intervención prevista</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Algunas preocupaciones</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Se incluyen todas las solicitudes 2013-2018. Solo 73,1% respondieron con información médica.</t>
+          <t>"This was a prospective, double blind, randomized study." No se detalla el cegamiento de participantes/personal respecto a la asignación; la terapia fágica tópica personalizada podría diferir en apariencia de la convencional.</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ROBINS-I</t>
+          <t>RoB 2 (adaptado)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sesgo en la clasificación de las intervenciones</t>
+          <t>Datos de desenlace faltantes</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>No hay intervención terapéutica como resultado principal.</t>
+          <t>"Four patients were excluded from each group as the patients died before the 28 days, and 34 patients in each group were analyzed." No se reporta análisis por intención de tratar.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4502,32 +4502,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>ROBINS-I</t>
+          <t>RoB 2 (adaptado)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sesgo por desviaciones de las intervenciones previstas</t>
+          <t>Medición del desenlace</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Sin información para juzgar</t>
+          <t>Algunas preocupaciones</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>No se evalúa adherencia a un tratamiento.</t>
+          <t>"Healing was assessed using the Pressure Ulcer Scale for Healing (PUSH) tool... at baseline and on days 5, 7, 14, 21, and 28." No se menciona cegamiento de evaluadores; la clasificación de tejidos tiene componente subjetivo.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4569,32 +4569,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ROBINS-I</t>
+          <t>RoB 2 (adaptado)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sesgo por datos faltantes</t>
+          <t>Selección del resultado notificado</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Algunas preocupaciones</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>26,9% de los solicitantes no respondió con la información médica solicitada.</t>
+          <t>"The clinical trial was registered with registration number CTRI/2024/03/064013." Endpoint primario preespecificado: evaluar eficacia de terapia fágica para úlceras por presión.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4636,42 +4636,42 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-132</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>Rc63b7d8aac</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ROBINS-I</t>
+          <t>RoB 2 (adaptado)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>GLOBAL</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Sesgo en la medición de los desenlaces</t>
+          <t>Juicio global del estudio</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>dominio</t>
+          <t>global</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Algunas preocupaciones</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Clasificación de razones de rechazo realizada por el propio equipo del hospital.</t>
+          <t>[DATO FALTANTE]</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4723,12 +4723,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sesgo en la selección del resultado notificado</t>
+          <t>Sesgo por confusión</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Bajo riesgo de sesgo</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Se reportan las 260 solicitudes y se explican las razones de rechazo.</t>
+          <t>Sin grupo control + antibióticos concomitantes frecuentes.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EST-116</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rb9ec93cff9</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Processing Phage Therapy Requests in a Brussels Military Hospital: Les (Viruses, 2019)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4790,22 +4790,22 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Juicio global del estudio</t>
+          <t>Sesgo en la selección de los participantes</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>dominio</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Sin información para juzgar</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>[DATO FALTANTE]</t>
+          <t>“Fifty requests for phage therapy were received. Customized phages were generated for 12 patients.”</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -4837,32 +4837,32 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Proceso de aleatorización</t>
+          <t>Sesgo en la clasificación de las intervenciones</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>"Randomization was performed using computer-generated random numbers. Patients were allocated to either conventional therapy or conventional therapy plus topical bacteriophage therapy. Group allocation was done using sealed opaque envelopes."</t>
+          <t>Fagos personalizados claramente caracterizados.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4904,32 +4904,32 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Desviaciones de la intervención prevista</t>
+          <t>Sesgo por desviaciones de las intervenciones previstas</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Algunas preocupaciones</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>"This was a prospective, double blind, randomized study." No se detalla el cegamiento de participantes/personal respecto a la asignación; la terapia fágica tópica personalizada podría diferir en apariencia de la convencional.</t>
+          <t>Tratamientos individualizados + co-intervenciones.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4971,32 +4971,32 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Datos de desenlace faltantes</t>
+          <t>Sesgo por datos faltantes</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Bajo riesgo de sesgo</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>"Four patients were excluded from each group as the patients died before the 28 days, and 34 patients in each group were analyzed." No se reporta análisis por intención de tratar.</t>
+          <t>Algunos datos inmunológicos solo en subgrupos.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5038,32 +5038,32 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Medición del desenlace</t>
+          <t>Sesgo en la medición de los desenlaces</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Algunas preocupaciones</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>"Healing was assessed using the Pressure Ulcer Scale for Healing (PUSH) tool... at baseline and on days 5, 7, 14, 21, and 28." No se menciona cegamiento de evaluadores; la clasificación de tejidos tiene componente subjetivo.</t>
+          <t>“These responses were determined by a combination of physician judgment and patient symptom reporting.”</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5105,32 +5105,32 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Selección del resultado notificado</t>
+          <t>Sesgo en la selección del resultado notificado</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Algunas preocupaciones</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>"The clinical trial was registered with registration number CTRI/2024/03/064013." Endpoint primario preespecificado: evaluar eficacia de terapia fágica para úlceras por presión.</t>
+          <t>Se reportan resultados favorables y desfavorables.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5172,22 +5172,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Algunas preocupaciones</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5239,17 +5239,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Sin grupo control + antibióticos concomitantes frecuentes.</t>
+          <t>Sin grupo control. No se puede separar el efecto del fago de otros tratamientos concurrentes.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5306,17 +5306,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Riesgo grave</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>“Fifty requests for phage therapy were received. Customized phages were generated for 12 patients.”</t>
+          <t>Pacientes seleccionados de la Unidad de Terapia Fágica (infecciones óseas, tejidos blandos o vías respiratorias altas).</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Fagos personalizados claramente caracterizados.</t>
+          <t>Fagos Staph_1N o Staph_A5L, vía local o local+oral, claramente descritos.</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5440,17 +5440,17 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Tratamientos individualizados + co-intervenciones.</t>
+          <t>Tratamientos personalizados, duración variable (hasta 8 semanas).</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5507,17 +5507,17 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Algunos datos inmunológicos solo en subgrupos.</t>
+          <t>Se reportan los 27 pacientes. Algunos datos de seguimiento incompletos.</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5574,17 +5574,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5619,7 +5619,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>“These responses were determined by a combination of physician judgment and patient symptom reporting.”</t>
+          <t>Tasa K (laboratorio objetivo). Resultados clínicos descriptivos y abiertos.</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -5641,17 +5641,17 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Se reportan resultados favorables y desfavorables.</t>
+          <t>Enfoque principal en el timing de aparición de anticuerpos.</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5708,17 +5708,17 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5767,544 +5767,8 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Sesgo por confusión</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Riesgo grave</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Sin grupo control. No se puede separar el efecto del fago de otros tratamientos concurrentes.</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Sesgo en la selección de los participantes</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>Riesgo moderado</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Pacientes seleccionados de la Unidad de Terapia Fágica (infecciones óseas, tejidos blandos o vías respiratorias altas).</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Sesgo en la clasificación de las intervenciones</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>Bajo riesgo de sesgo</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Fagos Staph_1N o Staph_A5L, vía local o local+oral, claramente descritos.</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Sesgo por desviaciones de las intervenciones previstas</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Riesgo moderado</t>
-        </is>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Tratamientos personalizados, duración variable (hasta 8 semanas).</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Sesgo por datos faltantes</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>Riesgo moderado</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Se reportan los 27 pacientes. Algunos datos de seguimiento incompletos.</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Sesgo en la medición de los desenlaces</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Riesgo grave</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Tasa K (laboratorio objetivo). Resultados clínicos descriptivos y abiertos.</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>D7</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Sesgo en la selección del resultado notificado</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Riesgo moderado</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Enfoque principal en el timing de aparición de anticuerpos.</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>GLOBAL</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Juicio global del estudio</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Riesgo grave</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>[DATO FALTANTE]</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M83"/>
+  <autoFilter ref="A1:M75"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
+++ b/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$M$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$M$69</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>74 filas de datos</t>
+          <t>68 filas de datos</t>
         </is>
       </c>
     </row>
@@ -709,7 +709,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4301,32 +4301,32 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Proceso de aleatorización</t>
+          <t>Sesgo por confusión</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Bajo riesgo de sesgo</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>"Randomization was performed using computer-generated random numbers. Patients were allocated to either conventional therapy or conventional therapy plus topical bacteriophage therapy. Group allocation was done using sealed opaque envelopes."</t>
+          <t>Sin grupo control + antibióticos concomitantes frecuentes.</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4368,32 +4368,32 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Desviaciones de la intervención prevista</t>
+          <t>Sesgo en la selección de los participantes</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Algunas preocupaciones</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>"This was a prospective, double blind, randomized study." No se detalla el cegamiento de participantes/personal respecto a la asignación; la terapia fágica tópica personalizada podría diferir en apariencia de la convencional.</t>
+          <t>“Fifty requests for phage therapy were received. Customized phages were generated for 12 patients.”</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Datos de desenlace faltantes</t>
+          <t>Sesgo en la clasificación de las intervenciones</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>"Four patients were excluded from each group as the patients died before the 28 days, and 34 patients in each group were analyzed." No se reporta análisis por intención de tratar.</t>
+          <t>Fagos personalizados claramente caracterizados.</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4502,32 +4502,32 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Medición del desenlace</t>
+          <t>Sesgo por desviaciones de las intervenciones previstas</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Algunas preocupaciones</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>"Healing was assessed using the Pressure Ulcer Scale for Healing (PUSH) tool... at baseline and on days 5, 7, 14, 21, and 28." No se menciona cegamiento de evaluadores; la clasificación de tejidos tiene componente subjetivo.</t>
+          <t>Tratamientos individualizados + co-intervenciones.</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4569,32 +4569,32 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Selección del resultado notificado</t>
+          <t>Sesgo por datos faltantes</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Algunas preocupaciones</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>"The clinical trial was registered with registration number CTRI/2024/03/064013." Endpoint primario preespecificado: evaluar eficacia de terapia fágica para úlceras por presión.</t>
+          <t>Algunos datos inmunológicos solo en subgrupos.</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4636,42 +4636,42 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EST-132</t>
+          <t>EST-146</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Rc63b7d8aac</t>
+          <t>R3405f1429d</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the  (Indian Journal of Critical Care Medicine, 2026)</t>
+          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RoB 2 (adaptado)</t>
+          <t>ROBINS-I</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Juicio global del estudio</t>
+          <t>Sesgo en la medición de los desenlaces</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>dominio</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Algunas preocupaciones</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>[DATO FALTANTE]</t>
+          <t>“These responses were determined by a combination of physician judgment and patient symptom reporting.”</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4723,12 +4723,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Sesgo por confusión</t>
+          <t>Sesgo en la selección del resultado notificado</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Riesgo grave</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4748,7 +4748,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Sin grupo control + antibióticos concomitantes frecuentes.</t>
+          <t>Se reportan resultados favorables y desfavorables.</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4790,17 +4790,17 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>GLOBAL</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Sesgo en la selección de los participantes</t>
+          <t>Juicio global del estudio</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>dominio</t>
+          <t>global</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>“Fifty requests for phage therapy were received. Customized phages were generated for 12 patients.”</t>
+          <t>[DATO FALTANTE]</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4837,17 +4837,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Sesgo en la clasificación de las intervenciones</t>
+          <t>Sesgo por confusión</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Bajo riesgo de sesgo</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Fagos personalizados claramente caracterizados.</t>
+          <t>Sin grupo control. No se puede separar el efecto del fago de otros tratamientos concurrentes.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4904,17 +4904,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Sesgo por desviaciones de las intervenciones previstas</t>
+          <t>Sesgo en la selección de los participantes</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Tratamientos individualizados + co-intervenciones.</t>
+          <t>Pacientes seleccionados de la Unidad de Terapia Fágica (infecciones óseas, tejidos blandos o vías respiratorias altas).</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4971,17 +4971,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sesgo por datos faltantes</t>
+          <t>Sesgo en la clasificación de las intervenciones</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Bajo riesgo de sesgo</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Algunos datos inmunológicos solo en subgrupos.</t>
+          <t>Fagos Staph_1N o Staph_A5L, vía local o local+oral, claramente descritos.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5038,17 +5038,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5058,12 +5058,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Sesgo en la medición de los desenlaces</t>
+          <t>Sesgo por desviaciones de las intervenciones previstas</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Riesgo grave</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5083,7 +5083,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>“These responses were determined by a combination of physician judgment and patient symptom reporting.”</t>
+          <t>Tratamientos personalizados, duración variable (hasta 8 semanas).</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5105,17 +5105,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Sesgo en la selección del resultado notificado</t>
+          <t>Sesgo por datos faltantes</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Se reportan resultados favorables y desfavorables.</t>
+          <t>Se reportan los 27 pacientes. Algunos datos de seguimiento incompletos.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5172,17 +5172,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EST-146</t>
+          <t>EST-152</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>R3405f1429d</t>
+          <t>R157654d30f</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>A Retrospective, Observational Study of 12 Cases of Expanded-Access Cu (Clinical infectious diseases : an official publication of the Infectious Diseases Society of America, 2023)</t>
+          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5192,17 +5192,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Juicio global del estudio</t>
+          <t>Sesgo en la medición de los desenlaces</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>dominio</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>[DATO FALTANTE]</t>
+          <t>Tasa K (laboratorio objetivo). Resultados clínicos descriptivos y abiertos.</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sesgo por confusión</t>
+          <t>Sesgo en la selección del resultado notificado</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Riesgo grave</t>
+          <t>Riesgo moderado</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Sin grupo control. No se puede separar el efecto del fago de otros tratamientos concurrentes.</t>
+          <t>Enfoque principal en el timing de aparición de anticuerpos.</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5326,22 +5326,22 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>GLOBAL</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sesgo en la selección de los participantes</t>
+          <t>Juicio global del estudio</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>dominio</t>
+          <t>global</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Riesgo moderado</t>
+          <t>Riesgo grave</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Pacientes seleccionados de la Unidad de Terapia Fágica (infecciones óseas, tejidos blandos o vías respiratorias altas).</t>
+          <t>[DATO FALTANTE]</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5365,410 +5365,8 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Sesgo en la clasificación de las intervenciones</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Bajo riesgo de sesgo</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Fagos Staph_1N o Staph_A5L, vía local o local+oral, claramente descritos.</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>D4</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Sesgo por desviaciones de las intervenciones previstas</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>Riesgo moderado</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Tratamientos personalizados, duración variable (hasta 8 semanas).</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Sesgo por datos faltantes</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>Riesgo moderado</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Se reportan los 27 pacientes. Algunos datos de seguimiento incompletos.</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Sesgo en la medición de los desenlaces</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>Riesgo grave</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Tasa K (laboratorio objetivo). Resultados clínicos descriptivos y abiertos.</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>D7</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Sesgo en la selección del resultado notificado</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>Riesgo moderado</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Enfoque principal en el timing de aparición de anticuerpos.</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>EST-152</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>R157654d30f</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>The Appearance of Antiphage Antibodies in Sera of Patients Treated wit (Antibiotics, 2025)</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>ROBINS-I</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>GLOBAL</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Juicio global del estudio</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>Riesgo grave</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>riesgo_sesgo_comparativos_consenso.xlsx, columna «¿En qué frase te apoyaste?», firmado 2026-09-09</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>[DATO FALTANTE]</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Danny Javier Valdiviezo Verdugo y Nataly Elizabeth Trelles Avila</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:M75"/>
+  <autoFilter ref="A1:M69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
+++ b/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
@@ -709,7 +709,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
+++ b/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
@@ -709,7 +709,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
+++ b/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
@@ -709,7 +709,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-08</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
+++ b/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
@@ -709,7 +709,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-12</t>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
+++ b/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
@@ -709,7 +709,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
+++ b/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
@@ -709,7 +709,7 @@
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-15</t>
+          <t>Generado el 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
+++ b/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <b val="1"/>
       <color rgb="001F4E79"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -89,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -100,11 +104,14 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -472,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -499,7 +506,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Anexo del material suplementario.</t>
+          <t>Cada juicio de riesgo de sesgo, uno por fila, con lo que lo sostiene en el cuaderno firmado (una cita literal, una nota sin cita o nada, marcado como dato faltante), el cuaderno de que sale («Fuente documental»), quién lo firmó y cuándo. Los del cuaderno de consenso parten de dos cuadernos, uno a nombre de cada autor, sin independencia acreditada; el canal generó el de consenso con los juicios coincidentes ya escritos y los discrepantes en blanco. Las frases que el modelo de lenguaje localizó de forma automática y puso como comentario en los formularios están en S18b: acompañan a lo que sostiene cada juicio, no lo sustituyen.</t>
         </is>
       </c>
     </row>
@@ -514,200 +521,211 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Secciones 2.7 y 3.7, tabla 7.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Las secciones y tablas que se citan son las del informe extendido (manuscrito maestro). En el manuscrito preparado para la revista las secciones no van numeradas; allí la tabla 7 (riesgo de sesgo) es la Tabla 5.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Cuántas filas</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>68 filas de datos</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
-    </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Qué significa cada columna</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Nº de juicio</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>columna interna: n</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>columna interna: estudio</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>informe</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Informe</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>columna interna: informe</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>referencia_del_informe</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Referencia del informe</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>columna interna: referencia_del_informe</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>instrumento</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Instrumento</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>columna interna: instrumento</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Dominio (código)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>columna interna: item</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Dominio</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>columna interna: dominio</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>tipo_de_juicio</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Tipo de juicio</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>columna interna: tipo_de_juicio</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Juicio</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>columna interna: valor</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>fuente_documental</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Fuente documental</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>columna interna: fuente_documental</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>cita_que_lo_respalda</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Lo que lo sostiene (cita o nota)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>columna interna: cita_que_lo_respalda</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>firmado_por</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Firmado por</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>columna interna: firmado_por</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>columna interna: fecha</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>El CSV con los nombres internos acompaña a este fichero: es la copia reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>Generado el 2026-10-19</t>
         </is>
@@ -737,73 +755,73 @@
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="8" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="B1" s="8" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>Nº de juicio</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>Estudio</t>
         </is>
       </c>
-      <c r="C1" s="8" t="inlineStr">
-        <is>
-          <t>informe</t>
-        </is>
-      </c>
-      <c r="D1" s="8" t="inlineStr">
-        <is>
-          <t>referencia_del_informe</t>
-        </is>
-      </c>
-      <c r="E1" s="8" t="inlineStr">
-        <is>
-          <t>instrumento</t>
-        </is>
-      </c>
-      <c r="F1" s="8" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="G1" s="8" t="inlineStr">
-        <is>
-          <t>dominio</t>
-        </is>
-      </c>
-      <c r="H1" s="8" t="inlineStr">
-        <is>
-          <t>tipo_de_juicio</t>
-        </is>
-      </c>
-      <c r="I1" s="8" t="inlineStr">
-        <is>
-          <t>valor</t>
-        </is>
-      </c>
-      <c r="J1" s="8" t="inlineStr">
-        <is>
-          <t>fuente_documental</t>
-        </is>
-      </c>
-      <c r="K1" s="8" t="inlineStr">
-        <is>
-          <t>cita_que_lo_respalda</t>
-        </is>
-      </c>
-      <c r="L1" s="8" t="inlineStr">
-        <is>
-          <t>firmado_por</t>
-        </is>
-      </c>
-      <c r="M1" s="8" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
+        <is>
+          <t>Informe</t>
+        </is>
+      </c>
+      <c r="D1" s="9" t="inlineStr">
+        <is>
+          <t>Referencia del informe</t>
+        </is>
+      </c>
+      <c r="E1" s="9" t="inlineStr">
+        <is>
+          <t>Instrumento</t>
+        </is>
+      </c>
+      <c r="F1" s="9" t="inlineStr">
+        <is>
+          <t>Dominio (código)</t>
+        </is>
+      </c>
+      <c r="G1" s="9" t="inlineStr">
+        <is>
+          <t>Dominio</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t>Tipo de juicio</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>Juicio</t>
+        </is>
+      </c>
+      <c r="J1" s="9" t="inlineStr">
+        <is>
+          <t>Fuente documental</t>
+        </is>
+      </c>
+      <c r="K1" s="9" t="inlineStr">
+        <is>
+          <t>Lo que lo sostiene (cita o nota)</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>Firmado por</t>
+        </is>
+      </c>
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>

--- a/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
+++ b/verificables revisión sistemática/S18_cada_juicio_con_su_frase.xlsx
@@ -727,7 +727,7 @@
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-19</t>
+          <t>Generado el 2026-10-20</t>
         </is>
       </c>
     </row>
